--- a/ROCAUCK.xlsx
+++ b/ROCAUCK.xlsx
@@ -5,27 +5,39 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\OneDrive\Documents\Github\Outlier-Detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khodg\Documents\GitHub\Outlier-Detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2C3992-305B-41C8-87E7-7D26EA5C4266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59B3DB8-44F6-4FC0-BF22-A0615E8E57A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="kValue" sheetId="1" r:id="rId1"/>
+    <sheet name="Parameters" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>DataSet</t>
   </si>
@@ -76,6 +88,27 @@
   </si>
   <si>
     <t>Boxplot</t>
+  </si>
+  <si>
+    <t>Datasets</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Log Gamma</t>
+  </si>
+  <si>
+    <t>Log SkewNorm</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>Scale</t>
   </si>
 </sst>
 </file>
@@ -83,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -102,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -110,21 +143,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,13 +465,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,7 +500,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -470,7 +529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="2">
         <v>0.76061395830017497</v>
@@ -497,7 +556,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="2">
         <v>0.76042495623109896</v>
@@ -524,7 +583,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -553,7 +612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="2">
         <v>0.733843537414966</v>
@@ -580,7 +639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="2">
         <v>0.71386054421768697</v>
@@ -607,7 +666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -636,7 +695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="2">
         <v>0.81711538461538402</v>
@@ -663,7 +722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="2">
         <v>0.81288461538461498</v>
@@ -690,7 +749,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -719,7 +778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="2">
         <v>0.99859154929577398</v>
@@ -746,7 +805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="2">
         <v>0.99812206572769901</v>
@@ -773,7 +832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -802,7 +861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="2">
         <v>0.64998061025625498</v>
@@ -829,7 +888,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="2">
         <v>0.64986716965342495</v>
@@ -856,7 +915,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,7 +944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="2">
         <v>0.53128082288290801</v>
@@ -912,7 +971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="2">
         <v>0.52740594617443903</v>
@@ -939,7 +998,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
@@ -968,7 +1027,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="2">
         <v>0.699277777777777</v>
@@ -995,7 +1054,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="2">
         <v>0.69872222222222202</v>
@@ -1022,7 +1081,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1051,7 +1110,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="B24" s="2">
         <v>0.87262872628726296</v>
@@ -1078,7 +1137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
       <c r="B25" s="2">
         <v>0.87181571815718095</v>
@@ -1105,7 +1164,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
@@ -1134,7 +1193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
       <c r="B27" s="2">
         <v>0.78358208955223796</v>
@@ -1161,7 +1220,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
       <c r="B28" s="2">
         <v>0.78300803673937902</v>
@@ -1188,7 +1247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -1217,7 +1276,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
       <c r="B30" s="2">
         <v>0.73547388059701502</v>
@@ -1244,7 +1303,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
       <c r="B31" s="2">
         <v>0.73542164179104397</v>
@@ -1271,7 +1330,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
@@ -1300,7 +1359,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="B33" s="2">
         <v>0.98258021933387496</v>
@@ -1327,7 +1386,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="2">
         <v>0.98247359870024298</v>
@@ -1357,4 +1416,424 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D48F05FF-AC1E-4268-842F-73B6602C8547}">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.46484375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="C3" s="7">
+        <v>9.34</v>
+      </c>
+      <c r="D3" s="7">
+        <v>3.52</v>
+      </c>
+      <c r="E3" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="F3" s="7">
+        <v>2.21</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.156</v>
+      </c>
+      <c r="H3" s="7">
+        <v>7.54</v>
+      </c>
+      <c r="I3" s="7">
+        <v>2.33</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.46200000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2.99</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.44</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="E4" s="7">
+        <v>24.93</v>
+      </c>
+      <c r="F4" s="7">
+        <v>-1.54</v>
+      </c>
+      <c r="G4" s="7">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="H4" s="7">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="I4" s="7">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.55100000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="E5" s="7">
+        <v>148</v>
+      </c>
+      <c r="F5" s="7">
+        <v>-8.23</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1.03</v>
+      </c>
+      <c r="I5" s="7">
+        <v>-2.38</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="D6" s="7">
+        <v>4.38</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2.97</v>
+      </c>
+      <c r="F6" s="7">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="H6" s="7">
+        <v>10.54</v>
+      </c>
+      <c r="I6" s="7">
+        <v>-0.91100000000000003</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.84899999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="C7" s="7">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="E7" s="7">
+        <v>115.44</v>
+      </c>
+      <c r="F7" s="7">
+        <v>-11.54</v>
+      </c>
+      <c r="G7" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="H7" s="7">
+        <v>-3.16</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1.149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1.47</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2.94</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.16</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.157</v>
+      </c>
+      <c r="H8" s="7">
+        <v>7.89</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.35099999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7">
+        <v>3.93</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1.94</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="E9" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2.54</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-1.61</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.78</v>
+      </c>
+      <c r="F10" s="7">
+        <v>-2.64</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="H10" s="7">
+        <v>18.36</v>
+      </c>
+      <c r="I10" s="7">
+        <v>-2.2799999999999998</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1.85</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3.27</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E11" s="7">
+        <v>218.4</v>
+      </c>
+      <c r="F11" s="7">
+        <v>-1.77</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1.55E-2</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1.504</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2.17</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>6.24</v>
+      </c>
+      <c r="F12" s="7">
+        <v>-0.97699999999999998</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.114</v>
+      </c>
+      <c r="H12" s="7">
+        <v>4.13</v>
+      </c>
+      <c r="I12" s="7">
+        <v>-0.626</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.45300000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7">
+        <v>3.01</v>
+      </c>
+      <c r="C13" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="D13" s="7">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>8.43</v>
+      </c>
+      <c r="F13" s="7">
+        <v>3.42</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3.4740000000000002</v>
+      </c>
+      <c r="I13" s="7">
+        <v>4.03</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.53500000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>